--- a/6861.T_settings.xlsx
+++ b/6861.T_settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AverageProfit</t>
+          <t>ProfitPerTrade</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,12 +464,27 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>FinalCapital</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TotalCommission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AverageHoldDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MaxDrawdown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -478,7 +493,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -487,37 +502,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>11.04330255878021</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8494848122138621</v>
+      </c>
+      <c r="I2" t="n">
+        <v>110433.0255878021</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1110433.025587802</v>
+      </c>
+      <c r="K2" t="n">
+        <v>26116.18054161494</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11.61538461538461</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15.11356333817357</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -525,11 +541,11 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -538,33 +554,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>8.573110146503243</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.504300596853132</v>
+      </c>
+      <c r="I3" t="n">
+        <v>85731.10146503244</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1085731.101465032</v>
+      </c>
+      <c r="K3" t="n">
+        <v>32773.41756755641</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" t="n">
+        <v>17.56484069916492</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -572,11 +589,11 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -585,33 +602,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>7.678877882686653</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5906829140528195</v>
+      </c>
+      <c r="I4" t="n">
+        <v>76788.77882686653</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1076788.778826867</v>
+      </c>
+      <c r="K4" t="n">
+        <v>25771.05235954216</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10.76923076923077</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15.11356333817358</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -619,46 +637,47 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>7.632400018662004</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6360333348885003</v>
+      </c>
+      <c r="I5" t="n">
+        <v>76324.00018662005</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1076324.00018662</v>
+      </c>
+      <c r="K5" t="n">
+        <v>25396.53764761309</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8.660363654406728</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -666,11 +685,11 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -679,33 +698,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>7.167710735565749</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5973092279638125</v>
+      </c>
+      <c r="I6" t="n">
+        <v>71677.1073556575</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1071677.107355657</v>
+      </c>
+      <c r="K6" t="n">
+        <v>22349.60434703952</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14.88777787438412</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +733,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -726,33 +746,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>6.840576990987779</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7600641101097533</v>
+      </c>
+      <c r="I7" t="n">
+        <v>68405.7699098778</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1068405.769909878</v>
+      </c>
+      <c r="K7" t="n">
+        <v>18056.7188929093</v>
+      </c>
+      <c r="L7" t="n">
+        <v>13.44444444444444</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11.08028820214489</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -764,42 +785,43 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>4.709765674461179</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3622896672662446</v>
+      </c>
+      <c r="I8" t="n">
+        <v>47097.6567446118</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1047097.656744612</v>
+      </c>
+      <c r="K8" t="n">
+        <v>25088.04875351329</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11.38461538461539</v>
+      </c>
+      <c r="M8" t="n">
+        <v>15.11356333817356</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -820,33 +842,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4.212693330766959</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3510577775639132</v>
+      </c>
+      <c r="I9" t="n">
+        <v>42126.93330766959</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1042126.93330767</v>
+      </c>
+      <c r="K9" t="n">
+        <v>21760.9429487257</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.166666666666666</v>
+      </c>
+      <c r="M9" t="n">
+        <v>17.2346423918402</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -854,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -863,37 +886,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>4.212693330766959</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3510577775639132</v>
+      </c>
+      <c r="I10" t="n">
+        <v>42126.93330766959</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1042126.93330767</v>
+      </c>
+      <c r="K10" t="n">
+        <v>21760.9429487257</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.166666666666666</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17.2346423918402</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -901,46 +925,47 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3.603487807276938</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.400387534141882</v>
+      </c>
+      <c r="I11" t="n">
+        <v>36034.87807276938</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1036034.878072769</v>
+      </c>
+      <c r="K11" t="n">
+        <v>17956.87322787028</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.22222222222222</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8.558913045297469</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -948,7 +973,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -957,37 +982,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.49340955496321</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1244507962469341</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14934.0955496321</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1014934.095549632</v>
+      </c>
+      <c r="K12" t="n">
+        <v>24545.61709226313</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8.660363654406709</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -995,46 +1021,47 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.275424109527317</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.07502494761925396</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12754.24109527317</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1012754.241095273</v>
+      </c>
+      <c r="K13" t="n">
+        <v>31535.18755681597</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9.470588235294118</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21.62426897555056</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1042,11 +1069,11 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1055,33 +1082,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.275424109527317</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.07502494761925396</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12754.24109527317</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1012754.241095273</v>
+      </c>
+      <c r="K14" t="n">
+        <v>31535.18755681597</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9.470588235294118</v>
+      </c>
+      <c r="M14" t="n">
+        <v>21.62426897555056</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1089,46 +1117,47 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.7467494523466565</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.08297216137185072</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7467.494523466565</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1007467.494523467</v>
+      </c>
+      <c r="K15" t="n">
+        <v>17489.33597061211</v>
+      </c>
+      <c r="L15" t="n">
+        <v>13.11111111111111</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11.08028820214489</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1136,11 +1165,11 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1149,33 +1178,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.5297200804920983</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.04074769849939218</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5297.200804920984</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1005297.200804921</v>
+      </c>
+      <c r="K16" t="n">
+        <v>27304.77935943723</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10.84615384615385</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12.02230574519094</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1196,33 +1226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.1478602017020923</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.00924126260638077</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1478.602017020923</v>
+      </c>
+      <c r="J17" t="n">
+        <v>998521.3979829791</v>
+      </c>
+      <c r="K17" t="n">
+        <v>30825.22630609293</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9.8125</v>
+      </c>
+      <c r="M17" t="n">
+        <v>17.56484069916492</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1239,37 +1270,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-3.36419330789306</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.3058357552630054</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-33641.9330789306</v>
+      </c>
+      <c r="J18" t="n">
+        <v>966358.0669210694</v>
+      </c>
+      <c r="K18" t="n">
+        <v>21986.59744548723</v>
+      </c>
+      <c r="L18" t="n">
+        <v>11.18181818181818</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12.08311036004389</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1281,7 +1313,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1290,33 +1322,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-3.36419330789306</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.3058357552630054</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-33641.9330789306</v>
+      </c>
+      <c r="J19" t="n">
+        <v>966358.0669210694</v>
+      </c>
+      <c r="K19" t="n">
+        <v>21986.59744548723</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11.18181818181818</v>
+      </c>
+      <c r="M19" t="n">
+        <v>12.08311036004389</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1324,46 +1357,47 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-5.010521360194066</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.7157887657420094</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-50105.21360194066</v>
+      </c>
+      <c r="J20" t="n">
+        <v>949894.7863980593</v>
+      </c>
+      <c r="K20" t="n">
+        <v>13428.76809535994</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10.84298754779554</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1380,37 +1414,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-6.050807007869961</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5500733643518146</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-60508.07007869962</v>
+      </c>
+      <c r="J21" t="n">
+        <v>939491.9299213004</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20901.97857636049</v>
+      </c>
+      <c r="L21" t="n">
+        <v>10.81818181818182</v>
+      </c>
+      <c r="M21" t="n">
+        <v>12.60494212411783</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1418,11 +1453,11 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1431,33 +1466,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-6.292095172636595</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.5720086520578723</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-62920.95172636595</v>
+      </c>
+      <c r="J22" t="n">
+        <v>937079.048273634</v>
+      </c>
+      <c r="K22" t="n">
+        <v>21764.52102710899</v>
+      </c>
+      <c r="L22" t="n">
+        <v>10.18181818181818</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12.08311036004388</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1465,46 +1501,47 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-6.292095172636595</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.5720086520578723</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-62920.95172636595</v>
+      </c>
+      <c r="J23" t="n">
+        <v>937079.048273634</v>
+      </c>
+      <c r="K23" t="n">
+        <v>21764.52102710899</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10.18181818181818</v>
+      </c>
+      <c r="M23" t="n">
+        <v>12.08311036004388</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1512,46 +1549,47 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-6.389998862192325</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.425999924146155</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-63899.98862192326</v>
+      </c>
+      <c r="J24" t="n">
+        <v>936100.0113780767</v>
+      </c>
+      <c r="K24" t="n">
+        <v>27230.53419201517</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>19.29275911118787</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1559,46 +1597,47 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-6.796023705564043</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.3997661003272966</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-67960.23705564043</v>
+      </c>
+      <c r="J25" t="n">
+        <v>932039.7629443596</v>
+      </c>
+      <c r="K25" t="n">
+        <v>32396.86090537824</v>
+      </c>
+      <c r="L25" t="n">
+        <v>10</v>
+      </c>
+      <c r="M25" t="n">
+        <v>17.84431405584932</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1615,37 +1654,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-6.859370679618279</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.4287106674761424</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-68593.70679618279</v>
+      </c>
+      <c r="J26" t="n">
+        <v>931406.2932038172</v>
+      </c>
+      <c r="K26" t="n">
+        <v>29717.94297401865</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M26" t="n">
+        <v>21.51612350296146</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1657,7 +1697,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1666,33 +1706,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-6.859370679618279</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.4287106674761424</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-68593.70679618279</v>
+      </c>
+      <c r="J27" t="n">
+        <v>931406.2932038172</v>
+      </c>
+      <c r="K27" t="n">
+        <v>29717.94297401865</v>
+      </c>
+      <c r="L27" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M27" t="n">
+        <v>21.51612350296146</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1700,11 +1741,11 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1713,33 +1754,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-7.629739039911039</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.089962719987291</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-76297.39039911039</v>
+      </c>
+      <c r="J28" t="n">
+        <v>923702.6096008896</v>
+      </c>
+      <c r="K28" t="n">
+        <v>13086.0877505569</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10.14285714285714</v>
+      </c>
+      <c r="M28" t="n">
+        <v>13.30138216822568</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1747,46 +1789,47 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-7.629739039911039</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-1.089962719987291</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-76297.39039911039</v>
+      </c>
+      <c r="J29" t="n">
+        <v>923702.6096008896</v>
+      </c>
+      <c r="K29" t="n">
+        <v>13086.0877505569</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10.14285714285714</v>
+      </c>
+      <c r="M29" t="n">
+        <v>13.30138216822568</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1794,46 +1837,47 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-8.875975035623997</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.8069068214203633</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-88759.75035623997</v>
+      </c>
+      <c r="J30" t="n">
+        <v>911240.24964376</v>
+      </c>
+      <c r="K30" t="n">
+        <v>21191.99257949259</v>
+      </c>
+      <c r="L30" t="n">
+        <v>10.90909090909091</v>
+      </c>
+      <c r="M30" t="n">
+        <v>12.08311036004389</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1841,46 +1885,47 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-8.875975035623997</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.8069068214203633</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-88759.75035623997</v>
+      </c>
+      <c r="J31" t="n">
+        <v>911240.24964376</v>
+      </c>
+      <c r="K31" t="n">
+        <v>21191.99257949259</v>
+      </c>
+      <c r="L31" t="n">
+        <v>10.90909090909091</v>
+      </c>
+      <c r="M31" t="n">
+        <v>12.08311036004389</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1892,42 +1937,43 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-12.36555393700085</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-1.124141267000077</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-123655.5393700085</v>
+      </c>
+      <c r="J32" t="n">
+        <v>876344.4606299915</v>
+      </c>
+      <c r="K32" t="n">
+        <v>20180.16101962093</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" t="n">
+        <v>12.86406189750717</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1935,11 +1981,11 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1948,33 +1994,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-12.36555393700085</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-1.124141267000077</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-123655.5393700085</v>
+      </c>
+      <c r="J33" t="n">
+        <v>876344.4606299915</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20180.16101962093</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" t="n">
+        <v>12.86406189750717</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1982,7 +2029,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1991,37 +2038,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-12.68194718441401</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.8454631456276006</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-126819.4718441401</v>
+      </c>
+      <c r="J34" t="n">
+        <v>873180.5281558599</v>
+      </c>
+      <c r="K34" t="n">
+        <v>26190.05421696624</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M34" t="n">
+        <v>24.71745500616962</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2038,37 +2086,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-12.68194718441401</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.8454631456276006</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-126819.4718441401</v>
+      </c>
+      <c r="J35" t="n">
+        <v>873180.5281558599</v>
+      </c>
+      <c r="K35" t="n">
+        <v>26190.05421696624</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>24.71745500616962</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2080,42 +2129,43 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-12.91690512044379</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1.43521168004931</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-129169.0512044379</v>
+      </c>
+      <c r="J36" t="n">
+        <v>870830.9487955621</v>
+      </c>
+      <c r="K36" t="n">
+        <v>16384.74551642162</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="M36" t="n">
+        <v>15.63477999991894</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2127,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2136,33 +2186,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-12.91690512044379</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.43521168004931</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-129169.0512044379</v>
+      </c>
+      <c r="J37" t="n">
+        <v>870830.9487955621</v>
+      </c>
+      <c r="K37" t="n">
+        <v>16384.74551642162</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="M37" t="n">
+        <v>15.63477999991894</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2170,46 +2221,47 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-13.06068127571881</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.76827536915993</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-130606.8127571881</v>
+      </c>
+      <c r="J38" t="n">
+        <v>869393.1872428119</v>
+      </c>
+      <c r="K38" t="n">
+        <v>31183.22843357671</v>
+      </c>
+      <c r="L38" t="n">
+        <v>9.470588235294118</v>
+      </c>
+      <c r="M38" t="n">
+        <v>21.88997997578124</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2221,42 +2273,43 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-14.99495504139734</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-1.249579586783112</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-149949.5504139734</v>
+      </c>
+      <c r="J39" t="n">
+        <v>850050.4495860266</v>
+      </c>
+      <c r="K39" t="n">
+        <v>21827.08357011764</v>
+      </c>
+      <c r="L39" t="n">
+        <v>10</v>
+      </c>
+      <c r="M39" t="n">
+        <v>16.56435870157542</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2264,11 +2317,11 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2277,33 +2330,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-15.318114022515</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-1.702012669168334</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-153181.14022515</v>
+      </c>
+      <c r="J40" t="n">
+        <v>846818.85977485</v>
+      </c>
+      <c r="K40" t="n">
+        <v>15960.5577411857</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8.555555555555555</v>
+      </c>
+      <c r="M40" t="n">
+        <v>17.96104685538125</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2315,42 +2369,43 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-15.318114022515</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.702012669168334</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-153181.14022515</v>
+      </c>
+      <c r="J41" t="n">
+        <v>846818.85977485</v>
+      </c>
+      <c r="K41" t="n">
+        <v>15960.5577411857</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8.555555555555555</v>
+      </c>
+      <c r="M41" t="n">
+        <v>17.96104685538125</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2358,46 +2413,47 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-15.318114022515</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-1.702012669168334</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-153181.14022515</v>
+      </c>
+      <c r="J42" t="n">
+        <v>846818.85977485</v>
+      </c>
+      <c r="K42" t="n">
+        <v>15960.5577411857</v>
+      </c>
+      <c r="L42" t="n">
+        <v>8.555555555555555</v>
+      </c>
+      <c r="M42" t="n">
+        <v>17.96104685538125</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2409,7 +2465,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2418,33 +2474,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-15.318114022515</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-1.702012669168334</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-153181.14022515</v>
+      </c>
+      <c r="J43" t="n">
+        <v>846818.85977485</v>
+      </c>
+      <c r="K43" t="n">
+        <v>15960.5577411857</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8.555555555555555</v>
+      </c>
+      <c r="M43" t="n">
+        <v>17.96104685538125</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2452,7 +2509,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2461,37 +2518,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-16.26066067849827</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.9033700376943484</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-162606.6067849827</v>
+      </c>
+      <c r="J44" t="n">
+        <v>837393.3932150173</v>
+      </c>
+      <c r="K44" t="n">
+        <v>32721.84251268191</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9.055555555555555</v>
+      </c>
+      <c r="M44" t="n">
+        <v>24.76497898538796</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2499,7 +2557,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2508,37 +2566,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-17.33886428070341</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-1.444905356725284</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-173388.6428070341</v>
+      </c>
+      <c r="J45" t="n">
+        <v>826611.3571929659</v>
+      </c>
+      <c r="K45" t="n">
+        <v>21252.83003756465</v>
+      </c>
+      <c r="L45" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="M45" t="n">
+        <v>18.8649935712122</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2546,46 +2605,47 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-17.33886428070341</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-1.444905356725284</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-173388.6428070341</v>
+      </c>
+      <c r="J46" t="n">
+        <v>826611.3571929659</v>
+      </c>
+      <c r="K46" t="n">
+        <v>21252.83003756465</v>
+      </c>
+      <c r="L46" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="M46" t="n">
+        <v>18.8649935712122</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/6861.T_settings.xlsx
+++ b/6861.T_settings.xlsx
@@ -509,28 +509,28 @@
         <v>38.46153846153847</v>
       </c>
       <c r="F2" t="n">
-        <v>11.04330255878021</v>
+        <v>11.04330216796994</v>
       </c>
       <c r="G2" t="n">
         <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8494848122138621</v>
+        <v>0.8494847821515339</v>
       </c>
       <c r="I2" t="n">
-        <v>110433.0255878021</v>
+        <v>110433.0216796994</v>
       </c>
       <c r="J2" t="n">
-        <v>1110433.025587802</v>
+        <v>1110433.021679699</v>
       </c>
       <c r="K2" t="n">
-        <v>26116.18054161494</v>
+        <v>26116.17991696679</v>
       </c>
       <c r="L2" t="n">
         <v>11.61538461538461</v>
       </c>
       <c r="M2" t="n">
-        <v>15.11356333817357</v>
+        <v>15.11356333817356</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -557,28 +557,28 @@
         <v>41.17647058823529</v>
       </c>
       <c r="F3" t="n">
-        <v>8.573110146503243</v>
+        <v>8.573088044374391</v>
       </c>
       <c r="G3" t="n">
         <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>0.504300596853132</v>
+        <v>0.5042992967279053</v>
       </c>
       <c r="I3" t="n">
-        <v>85731.10146503244</v>
+        <v>85730.8804437439</v>
       </c>
       <c r="J3" t="n">
-        <v>1085731.101465032</v>
+        <v>1085730.880443744</v>
       </c>
       <c r="K3" t="n">
-        <v>32773.41756755641</v>
+        <v>32773.4183615359</v>
       </c>
       <c r="L3" t="n">
         <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>17.56484069916492</v>
+        <v>17.56485869007984</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -605,28 +605,28 @@
         <v>30.76923076923077</v>
       </c>
       <c r="F4" t="n">
-        <v>7.678877882686653</v>
+        <v>7.678877503832336</v>
       </c>
       <c r="G4" t="n">
         <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5906829140528195</v>
+        <v>0.5906828849101797</v>
       </c>
       <c r="I4" t="n">
-        <v>76788.77882686653</v>
+        <v>76788.77503832337</v>
       </c>
       <c r="J4" t="n">
-        <v>1076788.778826867</v>
+        <v>1076788.775038323</v>
       </c>
       <c r="K4" t="n">
-        <v>25771.05235954216</v>
+        <v>25771.05174634653</v>
       </c>
       <c r="L4" t="n">
         <v>10.76923076923077</v>
       </c>
       <c r="M4" t="n">
-        <v>15.11356333817358</v>
+        <v>15.11356333817356</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -653,28 +653,28 @@
         <v>41.66666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>7.632400018662004</v>
+        <v>7.632384347261604</v>
       </c>
       <c r="G5" t="n">
         <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6360333348885003</v>
+        <v>0.636032028938467</v>
       </c>
       <c r="I5" t="n">
-        <v>76324.00018662005</v>
+        <v>76323.84347261605</v>
       </c>
       <c r="J5" t="n">
-        <v>1076324.00018662</v>
+        <v>1076323.843472616</v>
       </c>
       <c r="K5" t="n">
-        <v>25396.53764761309</v>
+        <v>25396.53393832815</v>
       </c>
       <c r="L5" t="n">
         <v>12.5</v>
       </c>
       <c r="M5" t="n">
-        <v>8.660363654406728</v>
+        <v>8.660363654406696</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -701,28 +701,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>7.167710735565749</v>
+        <v>7.167731843085703</v>
       </c>
       <c r="G6" t="n">
         <v>12</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5973092279638125</v>
+        <v>0.5973109869238086</v>
       </c>
       <c r="I6" t="n">
-        <v>71677.1073556575</v>
+        <v>71677.31843085703</v>
       </c>
       <c r="J6" t="n">
-        <v>1071677.107355657</v>
+        <v>1071677.318430857</v>
       </c>
       <c r="K6" t="n">
-        <v>22349.60434703952</v>
+        <v>22349.60927760968</v>
       </c>
       <c r="L6" t="n">
         <v>8.5</v>
       </c>
       <c r="M6" t="n">
-        <v>14.88777787438412</v>
+        <v>14.88774248843571</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -749,28 +749,28 @@
         <v>44.44444444444444</v>
       </c>
       <c r="F7" t="n">
-        <v>6.840576990987779</v>
+        <v>6.84056960582065</v>
       </c>
       <c r="G7" t="n">
         <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7600641101097533</v>
+        <v>0.7600632895356277</v>
       </c>
       <c r="I7" t="n">
-        <v>68405.7699098778</v>
+        <v>68405.69605820649</v>
       </c>
       <c r="J7" t="n">
-        <v>1068405.769909878</v>
+        <v>1068405.696058206</v>
       </c>
       <c r="K7" t="n">
-        <v>18056.7188929093</v>
+        <v>18056.71730205388</v>
       </c>
       <c r="L7" t="n">
         <v>13.44444444444444</v>
       </c>
       <c r="M7" t="n">
-        <v>11.08028820214489</v>
+        <v>11.08029409838116</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -797,28 +797,28 @@
         <v>30.76923076923077</v>
       </c>
       <c r="F8" t="n">
-        <v>4.709765674461179</v>
+        <v>4.709765306053241</v>
       </c>
       <c r="G8" t="n">
         <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3622896672662446</v>
+        <v>0.3622896389271724</v>
       </c>
       <c r="I8" t="n">
-        <v>47097.6567446118</v>
+        <v>47097.65306053241</v>
       </c>
       <c r="J8" t="n">
-        <v>1047097.656744612</v>
+        <v>1047097.653060532</v>
       </c>
       <c r="K8" t="n">
-        <v>25088.04875351329</v>
+        <v>25088.04815722578</v>
       </c>
       <c r="L8" t="n">
         <v>11.38461538461539</v>
       </c>
       <c r="M8" t="n">
-        <v>15.11356333817356</v>
+        <v>15.11356333817357</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -845,28 +845,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>4.212693330766959</v>
+        <v>4.212713856273075</v>
       </c>
       <c r="G9" t="n">
         <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3510577775639132</v>
+        <v>0.3510594880227562</v>
       </c>
       <c r="I9" t="n">
-        <v>42126.93330766959</v>
+        <v>42127.13856273075</v>
       </c>
       <c r="J9" t="n">
-        <v>1042126.93330767</v>
+        <v>1042127.138562731</v>
       </c>
       <c r="K9" t="n">
-        <v>21760.9429487257</v>
+        <v>21760.94774334146</v>
       </c>
       <c r="L9" t="n">
         <v>9.166666666666666</v>
       </c>
       <c r="M9" t="n">
-        <v>17.2346423918402</v>
+        <v>17.23460798161566</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -893,28 +893,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>4.212693330766959</v>
+        <v>4.212713856273075</v>
       </c>
       <c r="G10" t="n">
         <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3510577775639132</v>
+        <v>0.3510594880227562</v>
       </c>
       <c r="I10" t="n">
-        <v>42126.93330766959</v>
+        <v>42127.13856273075</v>
       </c>
       <c r="J10" t="n">
-        <v>1042126.93330767</v>
+        <v>1042127.138562731</v>
       </c>
       <c r="K10" t="n">
-        <v>21760.9429487257</v>
+        <v>21760.94774334146</v>
       </c>
       <c r="L10" t="n">
         <v>9.166666666666666</v>
       </c>
       <c r="M10" t="n">
-        <v>17.2346423918402</v>
+        <v>17.23460798161566</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -941,28 +941,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>3.603487807276938</v>
+        <v>3.603480645978567</v>
       </c>
       <c r="G11" t="n">
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>0.400387534141882</v>
+        <v>0.400386738442063</v>
       </c>
       <c r="I11" t="n">
-        <v>36034.87807276938</v>
+        <v>36034.80645978567</v>
       </c>
       <c r="J11" t="n">
-        <v>1036034.878072769</v>
+        <v>1036034.806459786</v>
       </c>
       <c r="K11" t="n">
-        <v>17956.87322787028</v>
+        <v>17956.87165776385</v>
       </c>
       <c r="L11" t="n">
         <v>12.22222222222222</v>
       </c>
       <c r="M11" t="n">
-        <v>8.558913045297469</v>
+        <v>8.558919108725291</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -989,28 +989,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>1.49340955496321</v>
+        <v>1.493394777515205</v>
       </c>
       <c r="G12" t="n">
         <v>12</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1244507962469341</v>
+        <v>0.1244495647929337</v>
       </c>
       <c r="I12" t="n">
-        <v>14934.0955496321</v>
+        <v>14933.94777515205</v>
       </c>
       <c r="J12" t="n">
-        <v>1014934.095549632</v>
+        <v>1014933.947775152</v>
       </c>
       <c r="K12" t="n">
-        <v>24545.61709226313</v>
+        <v>24545.61353324919</v>
       </c>
       <c r="L12" t="n">
         <v>12.25</v>
       </c>
       <c r="M12" t="n">
-        <v>8.660363654406709</v>
+        <v>8.660363654406718</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1037,28 +1037,28 @@
         <v>35.29411764705883</v>
       </c>
       <c r="F13" t="n">
-        <v>1.275424109527317</v>
+        <v>1.275403492981801</v>
       </c>
       <c r="G13" t="n">
         <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07502494761925396</v>
+        <v>0.0750237348812824</v>
       </c>
       <c r="I13" t="n">
-        <v>12754.24109527317</v>
+        <v>12754.03492981801</v>
       </c>
       <c r="J13" t="n">
-        <v>1012754.241095273</v>
+        <v>1012754.034929818</v>
       </c>
       <c r="K13" t="n">
-        <v>31535.18755681597</v>
+        <v>31535.18845308276</v>
       </c>
       <c r="L13" t="n">
         <v>9.470588235294118</v>
       </c>
       <c r="M13" t="n">
-        <v>21.62426897555056</v>
+        <v>21.62429919632666</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1085,28 +1085,28 @@
         <v>35.29411764705883</v>
       </c>
       <c r="F14" t="n">
-        <v>1.275424109527317</v>
+        <v>1.275403492981801</v>
       </c>
       <c r="G14" t="n">
         <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07502494761925396</v>
+        <v>0.0750237348812824</v>
       </c>
       <c r="I14" t="n">
-        <v>12754.24109527317</v>
+        <v>12754.03492981801</v>
       </c>
       <c r="J14" t="n">
-        <v>1012754.241095273</v>
+        <v>1012754.034929818</v>
       </c>
       <c r="K14" t="n">
-        <v>31535.18755681597</v>
+        <v>31535.18845308276</v>
       </c>
       <c r="L14" t="n">
         <v>9.470588235294118</v>
       </c>
       <c r="M14" t="n">
-        <v>21.62426897555056</v>
+        <v>21.62429919632666</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1133,28 +1133,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7467494523466565</v>
+        <v>0.7467424885122804</v>
       </c>
       <c r="G15" t="n">
         <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08297216137185072</v>
+        <v>0.08297138761247561</v>
       </c>
       <c r="I15" t="n">
-        <v>7467.494523466565</v>
+        <v>7467.424885122804</v>
       </c>
       <c r="J15" t="n">
-        <v>1007467.494523467</v>
+        <v>1007467.424885123</v>
       </c>
       <c r="K15" t="n">
-        <v>17489.33597061211</v>
+        <v>17489.33444379943</v>
       </c>
       <c r="L15" t="n">
         <v>13.11111111111111</v>
       </c>
       <c r="M15" t="n">
-        <v>11.08028820214489</v>
+        <v>11.08029409838116</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1181,28 +1181,28 @@
         <v>38.46153846153847</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5297200804920983</v>
+        <v>0.5297054433574085</v>
       </c>
       <c r="G16" t="n">
         <v>13</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04074769849939218</v>
+        <v>0.0407465725659545</v>
       </c>
       <c r="I16" t="n">
-        <v>5297.200804920984</v>
+        <v>5297.054433574085</v>
       </c>
       <c r="J16" t="n">
-        <v>1005297.200804921</v>
+        <v>1005297.054433574</v>
       </c>
       <c r="K16" t="n">
-        <v>27304.77935943723</v>
+        <v>27304.77539497687</v>
       </c>
       <c r="L16" t="n">
         <v>10.84615384615385</v>
       </c>
       <c r="M16" t="n">
-        <v>12.02230574519094</v>
+        <v>12.02230574519093</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1229,28 +1229,28 @@
         <v>37.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1478602017020923</v>
+        <v>-0.1478908564784913</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.00924126260638077</v>
+        <v>-0.009243178529905709</v>
       </c>
       <c r="I17" t="n">
-        <v>-1478.602017020923</v>
+        <v>-1478.908564784913</v>
       </c>
       <c r="J17" t="n">
-        <v>998521.3979829791</v>
+        <v>998521.0914352151</v>
       </c>
       <c r="K17" t="n">
-        <v>30825.22630609293</v>
+        <v>30825.22640773222</v>
       </c>
       <c r="L17" t="n">
         <v>9.8125</v>
       </c>
       <c r="M17" t="n">
-        <v>17.56484069916492</v>
+        <v>17.56485869007982</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1277,28 +1277,28 @@
         <v>36.36363636363637</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.36419330789306</v>
+        <v>-3.364209917230683</v>
       </c>
       <c r="G18" t="n">
         <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3058357552630054</v>
+        <v>-0.3058372652027894</v>
       </c>
       <c r="I18" t="n">
-        <v>-33641.9330789306</v>
+        <v>-33642.09917230683</v>
       </c>
       <c r="J18" t="n">
-        <v>966358.0669210694</v>
+        <v>966357.9008276932</v>
       </c>
       <c r="K18" t="n">
-        <v>21986.59744548723</v>
+        <v>21986.59484210183</v>
       </c>
       <c r="L18" t="n">
         <v>11.18181818181818</v>
       </c>
       <c r="M18" t="n">
-        <v>12.08311036004389</v>
+        <v>12.08311036004388</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1325,28 +1325,28 @@
         <v>36.36363636363637</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.36419330789306</v>
+        <v>-3.364209917230683</v>
       </c>
       <c r="G19" t="n">
         <v>11</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3058357552630054</v>
+        <v>-0.3058372652027894</v>
       </c>
       <c r="I19" t="n">
-        <v>-33641.9330789306</v>
+        <v>-33642.09917230683</v>
       </c>
       <c r="J19" t="n">
-        <v>966358.0669210694</v>
+        <v>966357.9008276932</v>
       </c>
       <c r="K19" t="n">
-        <v>21986.59744548723</v>
+        <v>21986.59484210183</v>
       </c>
       <c r="L19" t="n">
         <v>11.18181818181818</v>
       </c>
       <c r="M19" t="n">
-        <v>12.08311036004389</v>
+        <v>12.08311036004388</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1373,28 +1373,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.010521360194066</v>
+        <v>-5.010542458832695</v>
       </c>
       <c r="G20" t="n">
         <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7157887657420094</v>
+        <v>-0.715791779833242</v>
       </c>
       <c r="I20" t="n">
-        <v>-50105.21360194066</v>
+        <v>-50105.42458832695</v>
       </c>
       <c r="J20" t="n">
-        <v>949894.7863980593</v>
+        <v>949894.5754116731</v>
       </c>
       <c r="K20" t="n">
-        <v>13428.76809535994</v>
+        <v>13428.76676301926</v>
       </c>
       <c r="L20" t="n">
         <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>10.84298754779554</v>
+        <v>10.84298784353713</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1421,28 +1421,28 @@
         <v>36.36363636363637</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.050807007869961</v>
+        <v>-6.050843233593041</v>
       </c>
       <c r="G21" t="n">
         <v>11</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5500733643518146</v>
+        <v>-0.5500766575993674</v>
       </c>
       <c r="I21" t="n">
-        <v>-60508.07007869962</v>
+        <v>-60508.43233593041</v>
       </c>
       <c r="J21" t="n">
-        <v>939491.9299213004</v>
+        <v>939491.5676640696</v>
       </c>
       <c r="K21" t="n">
-        <v>20901.97857636049</v>
+        <v>20901.97663318706</v>
       </c>
       <c r="L21" t="n">
         <v>10.81818181818182</v>
       </c>
       <c r="M21" t="n">
-        <v>12.60494212411783</v>
+        <v>12.60494735252068</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1469,22 +1469,22 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.292095172636595</v>
+        <v>-6.292111278639221</v>
       </c>
       <c r="G22" t="n">
         <v>11</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5720086520578723</v>
+        <v>-0.5720101162399293</v>
       </c>
       <c r="I22" t="n">
-        <v>-62920.95172636595</v>
+        <v>-62921.11278639222</v>
       </c>
       <c r="J22" t="n">
-        <v>937079.048273634</v>
+        <v>937078.8872136078</v>
       </c>
       <c r="K22" t="n">
-        <v>21764.52102710899</v>
+        <v>21764.51847564497</v>
       </c>
       <c r="L22" t="n">
         <v>10.18181818181818</v>
@@ -1517,22 +1517,22 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.292095172636595</v>
+        <v>-6.292111278639221</v>
       </c>
       <c r="G23" t="n">
         <v>11</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5720086520578723</v>
+        <v>-0.5720101162399293</v>
       </c>
       <c r="I23" t="n">
-        <v>-62920.95172636595</v>
+        <v>-62921.11278639222</v>
       </c>
       <c r="J23" t="n">
-        <v>937079.048273634</v>
+        <v>937078.8872136078</v>
       </c>
       <c r="K23" t="n">
-        <v>21764.52102710899</v>
+        <v>21764.51847564497</v>
       </c>
       <c r="L23" t="n">
         <v>10.18181818181818</v>
@@ -1565,28 +1565,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.389998862192325</v>
+        <v>-6.390034130741097</v>
       </c>
       <c r="G24" t="n">
         <v>15</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.425999924146155</v>
+        <v>-0.4260022753827398</v>
       </c>
       <c r="I24" t="n">
-        <v>-63899.98862192326</v>
+        <v>-63900.34130741097</v>
       </c>
       <c r="J24" t="n">
-        <v>936100.0113780767</v>
+        <v>936099.658692589</v>
       </c>
       <c r="K24" t="n">
-        <v>27230.53419201517</v>
+        <v>27230.5322613642</v>
       </c>
       <c r="L24" t="n">
         <v>9.4</v>
       </c>
       <c r="M24" t="n">
-        <v>19.29275911118787</v>
+        <v>19.29278951848652</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -1613,28 +1613,28 @@
         <v>35.29411764705883</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.796023705564043</v>
+        <v>-6.796042679006571</v>
       </c>
       <c r="G25" t="n">
         <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3997661003272966</v>
+        <v>-0.3997672164121512</v>
       </c>
       <c r="I25" t="n">
-        <v>-67960.23705564043</v>
+        <v>-67960.42679006571</v>
       </c>
       <c r="J25" t="n">
-        <v>932039.7629443596</v>
+        <v>932039.5732099343</v>
       </c>
       <c r="K25" t="n">
-        <v>32396.86090537824</v>
+        <v>32396.86176984051</v>
       </c>
       <c r="L25" t="n">
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>17.84431405584932</v>
+        <v>17.84433198577107</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -1661,28 +1661,28 @@
         <v>31.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.859370679618279</v>
+        <v>-6.859399273949558</v>
       </c>
       <c r="G26" t="n">
         <v>16</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4287106674761424</v>
+        <v>-0.4287124546218474</v>
       </c>
       <c r="I26" t="n">
-        <v>-68593.70679618279</v>
+        <v>-68593.99273949559</v>
       </c>
       <c r="J26" t="n">
-        <v>931406.2932038172</v>
+        <v>931406.0072605044</v>
       </c>
       <c r="K26" t="n">
-        <v>29717.94297401865</v>
+        <v>29717.94322448053</v>
       </c>
       <c r="L26" t="n">
         <v>9.25</v>
       </c>
       <c r="M26" t="n">
-        <v>21.51612350296146</v>
+        <v>21.51616188322803</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -1709,28 +1709,28 @@
         <v>31.25</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.859370679618279</v>
+        <v>-6.859399273949558</v>
       </c>
       <c r="G27" t="n">
         <v>16</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4287106674761424</v>
+        <v>-0.4287124546218474</v>
       </c>
       <c r="I27" t="n">
-        <v>-68593.70679618279</v>
+        <v>-68593.99273949559</v>
       </c>
       <c r="J27" t="n">
-        <v>931406.2932038172</v>
+        <v>931406.0072605044</v>
       </c>
       <c r="K27" t="n">
-        <v>29717.94297401865</v>
+        <v>29717.94322448053</v>
       </c>
       <c r="L27" t="n">
         <v>9.25</v>
       </c>
       <c r="M27" t="n">
-        <v>21.51612350296146</v>
+        <v>21.51616188322803</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -1757,28 +1757,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F28" t="n">
-        <v>-7.629739039911039</v>
+        <v>-7.629759556780756</v>
       </c>
       <c r="G28" t="n">
         <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.089962719987291</v>
+        <v>-1.089965650968679</v>
       </c>
       <c r="I28" t="n">
-        <v>-76297.39039911039</v>
+        <v>-76297.59556780756</v>
       </c>
       <c r="J28" t="n">
-        <v>923702.6096008896</v>
+        <v>923702.4044321924</v>
       </c>
       <c r="K28" t="n">
-        <v>13086.0877505569</v>
+        <v>13086.08645495387</v>
       </c>
       <c r="L28" t="n">
         <v>10.14285714285714</v>
       </c>
       <c r="M28" t="n">
-        <v>13.30138216822568</v>
+        <v>13.30138245581255</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -1805,28 +1805,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.629739039911039</v>
+        <v>-7.629759556780756</v>
       </c>
       <c r="G29" t="n">
         <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.089962719987291</v>
+        <v>-1.089965650968679</v>
       </c>
       <c r="I29" t="n">
-        <v>-76297.39039911039</v>
+        <v>-76297.59556780756</v>
       </c>
       <c r="J29" t="n">
-        <v>923702.6096008896</v>
+        <v>923702.4044321924</v>
       </c>
       <c r="K29" t="n">
-        <v>13086.0877505569</v>
+        <v>13086.08645495387</v>
       </c>
       <c r="L29" t="n">
         <v>10.14285714285714</v>
       </c>
       <c r="M29" t="n">
-        <v>13.30138216822568</v>
+        <v>13.30138245581255</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F30" t="n">
-        <v>-8.875975035623997</v>
+        <v>-8.87599069752345</v>
       </c>
       <c r="G30" t="n">
         <v>11</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.8069068214203633</v>
+        <v>-0.8069082452294046</v>
       </c>
       <c r="I30" t="n">
-        <v>-88759.75035623997</v>
+        <v>-88759.90697523451</v>
       </c>
       <c r="J30" t="n">
-        <v>911240.24964376</v>
+        <v>911240.0930247655</v>
       </c>
       <c r="K30" t="n">
-        <v>21191.99257949259</v>
+        <v>21191.99009838203</v>
       </c>
       <c r="L30" t="n">
         <v>10.90909090909091</v>
       </c>
       <c r="M30" t="n">
-        <v>12.08311036004389</v>
+        <v>12.08311036004388</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -1901,28 +1901,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F31" t="n">
-        <v>-8.875975035623997</v>
+        <v>-8.87599069752345</v>
       </c>
       <c r="G31" t="n">
         <v>11</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8069068214203633</v>
+        <v>-0.8069082452294046</v>
       </c>
       <c r="I31" t="n">
-        <v>-88759.75035623997</v>
+        <v>-88759.90697523451</v>
       </c>
       <c r="J31" t="n">
-        <v>911240.24964376</v>
+        <v>911240.0930247655</v>
       </c>
       <c r="K31" t="n">
-        <v>21191.99257949259</v>
+        <v>21191.99009838203</v>
       </c>
       <c r="L31" t="n">
         <v>10.90909090909091</v>
       </c>
       <c r="M31" t="n">
-        <v>12.08311036004389</v>
+        <v>12.08311036004388</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -1949,28 +1949,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F32" t="n">
-        <v>-12.36555393700085</v>
+        <v>-12.3655877278305</v>
       </c>
       <c r="G32" t="n">
         <v>11</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.124141267000077</v>
+        <v>-1.124144338893682</v>
       </c>
       <c r="I32" t="n">
-        <v>-123655.5393700085</v>
+        <v>-123655.877278305</v>
       </c>
       <c r="J32" t="n">
-        <v>876344.4606299915</v>
+        <v>876344.122721695</v>
       </c>
       <c r="K32" t="n">
-        <v>20180.16101962093</v>
+        <v>20180.15920838615</v>
       </c>
       <c r="L32" t="n">
         <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>12.86406189750717</v>
+        <v>12.86405673433356</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F33" t="n">
-        <v>-12.36555393700085</v>
+        <v>-12.3655877278305</v>
       </c>
       <c r="G33" t="n">
         <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.124141267000077</v>
+        <v>-1.124144338893682</v>
       </c>
       <c r="I33" t="n">
-        <v>-123655.5393700085</v>
+        <v>-123655.877278305</v>
       </c>
       <c r="J33" t="n">
-        <v>876344.4606299915</v>
+        <v>876344.122721695</v>
       </c>
       <c r="K33" t="n">
-        <v>20180.16101962093</v>
+        <v>20180.15920838615</v>
       </c>
       <c r="L33" t="n">
         <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>12.86406189750717</v>
+        <v>12.86405673433356</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2045,28 +2045,28 @@
         <v>26.66666666666667</v>
       </c>
       <c r="F34" t="n">
-        <v>-12.68194718441401</v>
+        <v>-12.6819800824053</v>
       </c>
       <c r="G34" t="n">
         <v>15</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8454631456276006</v>
+        <v>-0.84546533882702</v>
       </c>
       <c r="I34" t="n">
-        <v>-126819.4718441401</v>
+        <v>-126819.800824053</v>
       </c>
       <c r="J34" t="n">
-        <v>873180.5281558599</v>
+        <v>873180.199175947</v>
       </c>
       <c r="K34" t="n">
-        <v>26190.05421696624</v>
+        <v>26190.05249847395</v>
       </c>
       <c r="L34" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>24.71745500616962</v>
+        <v>24.71748336965723</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2093,28 +2093,28 @@
         <v>26.66666666666667</v>
       </c>
       <c r="F35" t="n">
-        <v>-12.68194718441401</v>
+        <v>-12.6819800824053</v>
       </c>
       <c r="G35" t="n">
         <v>15</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8454631456276006</v>
+        <v>-0.84546533882702</v>
       </c>
       <c r="I35" t="n">
-        <v>-126819.4718441401</v>
+        <v>-126819.800824053</v>
       </c>
       <c r="J35" t="n">
-        <v>873180.5281558599</v>
+        <v>873180.199175947</v>
       </c>
       <c r="K35" t="n">
-        <v>26190.05421696624</v>
+        <v>26190.05249847395</v>
       </c>
       <c r="L35" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>24.71745500616962</v>
+        <v>24.71748336965723</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2141,28 +2141,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F36" t="n">
-        <v>-12.91690512044379</v>
+        <v>-12.91688952466602</v>
       </c>
       <c r="G36" t="n">
         <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.43521168004931</v>
+        <v>-1.435209947185114</v>
       </c>
       <c r="I36" t="n">
-        <v>-129169.0512044379</v>
+        <v>-129168.8952466602</v>
       </c>
       <c r="J36" t="n">
-        <v>870830.9487955621</v>
+        <v>870831.1047533398</v>
       </c>
       <c r="K36" t="n">
-        <v>16384.74551642162</v>
+        <v>16384.74825947572</v>
       </c>
       <c r="L36" t="n">
         <v>7.666666666666667</v>
       </c>
       <c r="M36" t="n">
-        <v>15.63477999991894</v>
+        <v>15.63475592749013</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2189,28 +2189,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F37" t="n">
-        <v>-12.91690512044379</v>
+        <v>-12.91688952466602</v>
       </c>
       <c r="G37" t="n">
         <v>9</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.43521168004931</v>
+        <v>-1.435209947185114</v>
       </c>
       <c r="I37" t="n">
-        <v>-129169.0512044379</v>
+        <v>-129168.8952466602</v>
       </c>
       <c r="J37" t="n">
-        <v>870830.9487955621</v>
+        <v>870831.1047533398</v>
       </c>
       <c r="K37" t="n">
-        <v>16384.74551642162</v>
+        <v>16384.74825947572</v>
       </c>
       <c r="L37" t="n">
         <v>7.666666666666667</v>
       </c>
       <c r="M37" t="n">
-        <v>15.63477999991894</v>
+        <v>15.63475592749013</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2237,28 +2237,28 @@
         <v>29.41176470588236</v>
       </c>
       <c r="F38" t="n">
-        <v>-13.06068127571881</v>
+        <v>-13.06069897387113</v>
       </c>
       <c r="G38" t="n">
         <v>17</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.76827536915993</v>
+        <v>-0.7682764102277133</v>
       </c>
       <c r="I38" t="n">
-        <v>-130606.8127571881</v>
+        <v>-130606.9897387113</v>
       </c>
       <c r="J38" t="n">
-        <v>869393.1872428119</v>
+        <v>869393.0102612887</v>
       </c>
       <c r="K38" t="n">
-        <v>31183.22843357671</v>
+        <v>31183.22939545791</v>
       </c>
       <c r="L38" t="n">
         <v>9.470588235294118</v>
       </c>
       <c r="M38" t="n">
-        <v>21.88997997578124</v>
+        <v>21.89001009410224</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2285,28 +2285,28 @@
         <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>-14.99495504139734</v>
+        <v>-14.99494944320635</v>
       </c>
       <c r="G39" t="n">
         <v>12</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.249579586783112</v>
+        <v>-1.249579120267196</v>
       </c>
       <c r="I39" t="n">
-        <v>-149949.5504139734</v>
+        <v>-149949.4944320635</v>
       </c>
       <c r="J39" t="n">
-        <v>850050.4495860266</v>
+        <v>850050.5055679365</v>
       </c>
       <c r="K39" t="n">
-        <v>21827.08357011764</v>
+        <v>21827.08617678321</v>
       </c>
       <c r="L39" t="n">
         <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>16.56435870157542</v>
+        <v>16.56435320674091</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F40" t="n">
-        <v>-15.318114022515</v>
+        <v>-15.31809885677154</v>
       </c>
       <c r="G40" t="n">
         <v>9</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.702012669168334</v>
+        <v>-1.702010984085727</v>
       </c>
       <c r="I40" t="n">
-        <v>-153181.14022515</v>
+        <v>-153180.9885677154</v>
       </c>
       <c r="J40" t="n">
-        <v>846818.85977485</v>
+        <v>846819.0114322846</v>
       </c>
       <c r="K40" t="n">
-        <v>15960.5577411857</v>
+        <v>15960.56040860347</v>
       </c>
       <c r="L40" t="n">
         <v>8.555555555555555</v>
       </c>
       <c r="M40" t="n">
-        <v>17.96104685538125</v>
+        <v>17.96102344671994</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2381,28 +2381,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F41" t="n">
-        <v>-15.318114022515</v>
+        <v>-15.31809885677154</v>
       </c>
       <c r="G41" t="n">
         <v>9</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.702012669168334</v>
+        <v>-1.702010984085727</v>
       </c>
       <c r="I41" t="n">
-        <v>-153181.14022515</v>
+        <v>-153180.9885677154</v>
       </c>
       <c r="J41" t="n">
-        <v>846818.85977485</v>
+        <v>846819.0114322846</v>
       </c>
       <c r="K41" t="n">
-        <v>15960.5577411857</v>
+        <v>15960.56040860347</v>
       </c>
       <c r="L41" t="n">
         <v>8.555555555555555</v>
       </c>
       <c r="M41" t="n">
-        <v>17.96104685538125</v>
+        <v>17.96102344671994</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F42" t="n">
-        <v>-15.318114022515</v>
+        <v>-15.31809885677154</v>
       </c>
       <c r="G42" t="n">
         <v>9</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.702012669168334</v>
+        <v>-1.702010984085727</v>
       </c>
       <c r="I42" t="n">
-        <v>-153181.14022515</v>
+        <v>-153180.9885677154</v>
       </c>
       <c r="J42" t="n">
-        <v>846818.85977485</v>
+        <v>846819.0114322846</v>
       </c>
       <c r="K42" t="n">
-        <v>15960.5577411857</v>
+        <v>15960.56040860347</v>
       </c>
       <c r="L42" t="n">
         <v>8.555555555555555</v>
       </c>
       <c r="M42" t="n">
-        <v>17.96104685538125</v>
+        <v>17.96102344671994</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2477,28 +2477,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F43" t="n">
-        <v>-15.318114022515</v>
+        <v>-15.31809885677154</v>
       </c>
       <c r="G43" t="n">
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.702012669168334</v>
+        <v>-1.702010984085727</v>
       </c>
       <c r="I43" t="n">
-        <v>-153181.14022515</v>
+        <v>-153180.9885677154</v>
       </c>
       <c r="J43" t="n">
-        <v>846818.85977485</v>
+        <v>846819.0114322846</v>
       </c>
       <c r="K43" t="n">
-        <v>15960.5577411857</v>
+        <v>15960.56040860347</v>
       </c>
       <c r="L43" t="n">
         <v>8.555555555555555</v>
       </c>
       <c r="M43" t="n">
-        <v>17.96104685538125</v>
+        <v>17.96102344671994</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -2525,28 +2525,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F44" t="n">
-        <v>-16.26066067849827</v>
+        <v>-16.2606777252339</v>
       </c>
       <c r="G44" t="n">
         <v>18</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.9033700376943484</v>
+        <v>-0.9033709847352169</v>
       </c>
       <c r="I44" t="n">
-        <v>-162606.6067849827</v>
+        <v>-162606.7772523391</v>
       </c>
       <c r="J44" t="n">
-        <v>837393.3932150173</v>
+        <v>837393.2227476609</v>
       </c>
       <c r="K44" t="n">
-        <v>32721.84251268191</v>
+        <v>32721.84316134894</v>
       </c>
       <c r="L44" t="n">
         <v>9.055555555555555</v>
       </c>
       <c r="M44" t="n">
-        <v>24.76497898538796</v>
+        <v>24.76500799514258</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -2573,28 +2573,28 @@
         <v>25</v>
       </c>
       <c r="F45" t="n">
-        <v>-17.33886428070341</v>
+        <v>-17.33885883687568</v>
       </c>
       <c r="G45" t="n">
         <v>12</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.444905356725284</v>
+        <v>-1.444904903072973</v>
       </c>
       <c r="I45" t="n">
-        <v>-173388.6428070341</v>
+        <v>-173388.5883687568</v>
       </c>
       <c r="J45" t="n">
-        <v>826611.3571929659</v>
+        <v>826611.4116312432</v>
       </c>
       <c r="K45" t="n">
-        <v>21252.83003756465</v>
+        <v>21252.83257235462</v>
       </c>
       <c r="L45" t="n">
         <v>10.66666666666667</v>
       </c>
       <c r="M45" t="n">
-        <v>18.8649935712122</v>
+        <v>18.86498822789103</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -2621,28 +2621,28 @@
         <v>25</v>
       </c>
       <c r="F46" t="n">
-        <v>-17.33886428070341</v>
+        <v>-17.33885883687568</v>
       </c>
       <c r="G46" t="n">
         <v>12</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.444905356725284</v>
+        <v>-1.444904903072973</v>
       </c>
       <c r="I46" t="n">
-        <v>-173388.6428070341</v>
+        <v>-173388.5883687568</v>
       </c>
       <c r="J46" t="n">
-        <v>826611.3571929659</v>
+        <v>826611.4116312432</v>
       </c>
       <c r="K46" t="n">
-        <v>21252.83003756465</v>
+        <v>21252.83257235462</v>
       </c>
       <c r="L46" t="n">
         <v>10.66666666666667</v>
       </c>
       <c r="M46" t="n">
-        <v>18.8649935712122</v>
+        <v>18.86498822789103</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
